--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_001.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_001.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="140">
   <si>
     <t>Sezione</t>
   </si>
@@ -490,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.71875" customWidth="true" bestFit="true"/>
@@ -2689,19 +2689,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2715,7 +2715,7 @@
         <v>116</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>9</v>
@@ -2724,7 +2724,7 @@
         <v>118</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2738,7 +2738,7 @@
         <v>116</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>9</v>
@@ -2747,7 +2747,7 @@
         <v>118</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2761,7 +2761,7 @@
         <v>116</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>9</v>
@@ -2770,7 +2770,7 @@
         <v>118</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2784,7 +2784,7 @@
         <v>116</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
@@ -2793,7 +2793,7 @@
         <v>118</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2807,16 +2807,16 @@
         <v>116</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2830,7 +2830,7 @@
         <v>116</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>33</v>
@@ -2839,10 +2839,10 @@
         <v>118</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>18</v>
@@ -2853,7 +2853,7 @@
         <v>116</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>33</v>
@@ -2862,10 +2862,10 @@
         <v>118</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>18</v>
@@ -2876,7 +2876,7 @@
         <v>116</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>33</v>
@@ -2885,10 +2885,10 @@
         <v>118</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>18</v>
@@ -2899,7 +2899,7 @@
         <v>116</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>61</v>
+        <v>134</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>33</v>
@@ -2908,7 +2908,7 @@
         <v>118</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>12</v>
@@ -2919,24 +2919,47 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B107" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D107" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="E107" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G106" s="2" t="s">
+      <c r="F107" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" s="2" t="s">
         <v>18</v>
       </c>
     </row>
